--- a/notebooks/Random Forest/predictions_ele_2019.xlsx
+++ b/notebooks/Random Forest/predictions_ele_2019.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ОПЖ_прогноз</t>
+          <t>predictions</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ОПЖ_реальный</t>
+          <t>ОПЖ</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -492,16 +492,16 @@
         <v>2019</v>
       </c>
       <c r="C3" t="n">
-        <v>69.0886260918363</v>
+        <v>69.08862609183629</v>
       </c>
       <c r="D3" t="n">
         <v>68.42</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6686260918363018</v>
+        <v>-0.6686260918362876</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9772377840343494</v>
+        <v>-0.9772377840343285</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         <v>2019</v>
       </c>
       <c r="C4" t="n">
-        <v>71.53524152884545</v>
+        <v>71.53524152884543</v>
       </c>
       <c r="D4" t="n">
         <v>71.56</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02475847115455565</v>
+        <v>0.02475847115456986</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03459819893034607</v>
+        <v>0.03459819893036593</v>
       </c>
     </row>
     <row r="5">
@@ -580,16 +580,16 @@
         <v>2019</v>
       </c>
       <c r="C7" t="n">
-        <v>71.82096677778235</v>
+        <v>71.82096677778236</v>
       </c>
       <c r="D7" t="n">
         <v>72.14</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3190332222176551</v>
+        <v>0.3190332222176409</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4422417829465693</v>
+        <v>0.4422417829465496</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         <v>2019</v>
       </c>
       <c r="C8" t="n">
-        <v>71.57955732158439</v>
+        <v>71.57955732158437</v>
       </c>
       <c r="D8" t="n">
         <v>72</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4204426784156112</v>
+        <v>0.4204426784156254</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5839481644661266</v>
+        <v>0.5839481644661465</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         <v>2019</v>
       </c>
       <c r="C9" t="n">
-        <v>73.48758485913382</v>
+        <v>73.48758485913383</v>
       </c>
       <c r="D9" t="n">
         <v>74.11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6224151408661811</v>
+        <v>0.6224151408661669</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8398531114103105</v>
+        <v>0.8398531114102914</v>
       </c>
     </row>
     <row r="10">
@@ -690,16 +690,16 @@
         <v>2019</v>
       </c>
       <c r="C12" t="n">
-        <v>68.4151317929293</v>
+        <v>68.41513179292929</v>
       </c>
       <c r="D12" t="n">
         <v>67.91</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5051317929293049</v>
+        <v>-0.5051317929292907</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7438253466784052</v>
+        <v>-0.7438253466783842</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         <v>2019</v>
       </c>
       <c r="C13" t="n">
-        <v>72.29950102800582</v>
+        <v>72.29950102800579</v>
       </c>
       <c r="D13" t="n">
         <v>72.81999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5204989719941722</v>
+        <v>0.5204989719942006</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7147747486874104</v>
+        <v>0.7147747486874494</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         <v>2019</v>
       </c>
       <c r="C14" t="n">
-        <v>71.22669688708939</v>
+        <v>71.22669688708936</v>
       </c>
       <c r="D14" t="n">
         <v>71.41</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1833031129106075</v>
+        <v>0.1833031129106359</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2566910977602682</v>
+        <v>0.256691097760308</v>
       </c>
     </row>
     <row r="15">
@@ -822,16 +822,16 @@
         <v>2019</v>
       </c>
       <c r="C18" t="n">
-        <v>72.47643079026524</v>
+        <v>72.47643079026523</v>
       </c>
       <c r="D18" t="n">
         <v>72.79000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3135692097347658</v>
+        <v>0.31356920973478</v>
       </c>
       <c r="F18" t="n">
-        <v>0.430786110365113</v>
+        <v>0.4307861103651325</v>
       </c>
     </row>
     <row r="19">
@@ -866,16 +866,16 @@
         <v>2019</v>
       </c>
       <c r="C20" t="n">
-        <v>75.58304093736682</v>
+        <v>75.58304093736679</v>
       </c>
       <c r="D20" t="n">
         <v>75.7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1169590626331853</v>
+        <v>0.1169590626332138</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1545033852485936</v>
+        <v>0.1545033852486311</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         <v>2019</v>
       </c>
       <c r="C21" t="n">
-        <v>69.52122629767115</v>
+        <v>69.52122629767116</v>
       </c>
       <c r="D21" t="n">
         <v>69.69</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1687737023288491</v>
+        <v>0.1687737023288349</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2421777906856782</v>
+        <v>0.2421777906856578</v>
       </c>
     </row>
     <row r="22">
@@ -910,16 +910,16 @@
         <v>2019</v>
       </c>
       <c r="C22" t="n">
-        <v>72.21667802739212</v>
+        <v>72.21667802739213</v>
       </c>
       <c r="D22" t="n">
         <v>72.48</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2633219726078835</v>
+        <v>0.2633219726078693</v>
       </c>
       <c r="F22" t="n">
-        <v>0.363302942339795</v>
+        <v>0.3633029423397754</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         <v>2019</v>
       </c>
       <c r="C23" t="n">
-        <v>71.65509471031555</v>
+        <v>71.65509471031557</v>
       </c>
       <c r="D23" t="n">
         <v>71.83</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1749052896844461</v>
+        <v>0.1749052896844319</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2434989415069554</v>
+        <v>0.2434989415069356</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         <v>2019</v>
       </c>
       <c r="C24" t="n">
-        <v>74.24697293168809</v>
+        <v>74.24697293168808</v>
       </c>
       <c r="D24" t="n">
         <v>74.05</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1969729316880944</v>
+        <v>-0.1969729316880802</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2659999077489458</v>
+        <v>-0.2659999077489266</v>
       </c>
     </row>
     <row r="25">
@@ -1042,16 +1042,16 @@
         <v>2019</v>
       </c>
       <c r="C28" t="n">
-        <v>73.34150137629751</v>
+        <v>73.3415013762975</v>
       </c>
       <c r="D28" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5584986237024907</v>
+        <v>0.5584986237025049</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7557491525067532</v>
+        <v>0.7557491525067725</v>
       </c>
     </row>
     <row r="29">
@@ -1064,16 +1064,16 @@
         <v>2019</v>
       </c>
       <c r="C29" t="n">
-        <v>72.90873113986855</v>
+        <v>72.90873113986854</v>
       </c>
       <c r="D29" t="n">
         <v>73.38</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4712688601314454</v>
+        <v>0.4712688601314596</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6422306624849352</v>
+        <v>0.6422306624849545</v>
       </c>
     </row>
     <row r="30">
@@ -1086,16 +1086,16 @@
         <v>2019</v>
       </c>
       <c r="C30" t="n">
-        <v>69.10278077467223</v>
+        <v>69.1027807746722</v>
       </c>
       <c r="D30" t="n">
         <v>69.23</v>
       </c>
       <c r="E30" t="n">
-        <v>0.127219225327778</v>
+        <v>0.1272192253278064</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1837631450639578</v>
+        <v>0.1837631450639988</v>
       </c>
     </row>
     <row r="31">
@@ -1108,16 +1108,16 @@
         <v>2019</v>
       </c>
       <c r="C31" t="n">
-        <v>74.25632578592338</v>
+        <v>74.25632578592337</v>
       </c>
       <c r="D31" t="n">
         <v>74.67</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4136742140766216</v>
+        <v>0.4136742140766358</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5540032329940024</v>
+        <v>0.5540032329940215</v>
       </c>
     </row>
     <row r="32">
@@ -1130,16 +1130,16 @@
         <v>2019</v>
       </c>
       <c r="C32" t="n">
-        <v>71.08726215865062</v>
+        <v>71.0872621586506</v>
       </c>
       <c r="D32" t="n">
         <v>71.04000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.04726215865061079</v>
+        <v>-0.04726215865059658</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.06652893954196337</v>
+        <v>-0.06652893954194337</v>
       </c>
     </row>
     <row r="33">
@@ -1174,16 +1174,16 @@
         <v>2019</v>
       </c>
       <c r="C34" t="n">
-        <v>71.92378579969071</v>
+        <v>71.92378579969072</v>
       </c>
       <c r="D34" t="n">
         <v>72.19</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2662142003092924</v>
+        <v>0.2662142003092782</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3687688049720078</v>
+        <v>0.3687688049719881</v>
       </c>
     </row>
     <row r="35">
@@ -1218,16 +1218,16 @@
         <v>2019</v>
       </c>
       <c r="C36" t="n">
-        <v>72.11992631193874</v>
+        <v>72.11992631193876</v>
       </c>
       <c r="D36" t="n">
         <v>72.37</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2500736880612635</v>
+        <v>0.2500736880612493</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3455488297101886</v>
+        <v>0.345548829710169</v>
       </c>
     </row>
     <row r="37">
@@ -1240,16 +1240,16 @@
         <v>2019</v>
       </c>
       <c r="C37" t="n">
-        <v>72.12264213722318</v>
+        <v>72.1226421372232</v>
       </c>
       <c r="D37" t="n">
         <v>72.29000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1673578627768251</v>
+        <v>0.1673578627768109</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2315090092361669</v>
+        <v>0.2315090092361472</v>
       </c>
     </row>
     <row r="38">
@@ -1306,16 +1306,16 @@
         <v>2019</v>
       </c>
       <c r="C40" t="n">
-        <v>73.09701844711402</v>
+        <v>73.09701844711401</v>
       </c>
       <c r="D40" t="n">
         <v>73.34999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>0.25298155288597</v>
+        <v>0.2529815528859842</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3448964592855761</v>
+        <v>0.3448964592855954</v>
       </c>
     </row>
     <row r="41">
@@ -1416,16 +1416,16 @@
         <v>2019</v>
       </c>
       <c r="C45" t="n">
-        <v>70.09643433110722</v>
+        <v>70.09643433110718</v>
       </c>
       <c r="D45" t="n">
         <v>69.78</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.3164343311072173</v>
+        <v>-0.3164343311071747</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.4534742492221515</v>
+        <v>-0.4534742492220903</v>
       </c>
     </row>
     <row r="46">
@@ -1460,16 +1460,16 @@
         <v>2019</v>
       </c>
       <c r="C47" t="n">
-        <v>70.8029546918728</v>
+        <v>70.80295469187278</v>
       </c>
       <c r="D47" t="n">
         <v>70.70999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.09295469187280503</v>
+        <v>-0.09295469187279082</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1314590466310352</v>
+        <v>-0.1314590466310152</v>
       </c>
     </row>
     <row r="48">
@@ -1482,16 +1482,16 @@
         <v>2019</v>
       </c>
       <c r="C48" t="n">
-        <v>77.85820308802313</v>
+        <v>77.85820308802315</v>
       </c>
       <c r="D48" t="n">
         <v>79.03</v>
       </c>
       <c r="E48" t="n">
-        <v>1.17179691197687</v>
+        <v>1.171796911976855</v>
       </c>
       <c r="F48" t="n">
-        <v>1.482724170538871</v>
+        <v>1.482724170538853</v>
       </c>
     </row>
     <row r="49">
@@ -1592,16 +1592,16 @@
         <v>2019</v>
       </c>
       <c r="C53" t="n">
-        <v>72.50978715291157</v>
+        <v>72.50978715291158</v>
       </c>
       <c r="D53" t="n">
         <v>72.73999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2302128470884242</v>
+        <v>0.2302128470884099</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3164872794726755</v>
+        <v>0.316487279472656</v>
       </c>
     </row>
     <row r="54">
@@ -1636,16 +1636,16 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>73.87039848158528</v>
+        <v>73.87039848158527</v>
       </c>
       <c r="D55" t="n">
         <v>74.14</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2696015184147171</v>
+        <v>0.2696015184147313</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3636384116734788</v>
+        <v>0.3636384116734979</v>
       </c>
     </row>
     <row r="56">
@@ -1658,16 +1658,16 @@
         <v>2019</v>
       </c>
       <c r="C56" t="n">
-        <v>69.483612738978</v>
+        <v>69.48361273897795</v>
       </c>
       <c r="D56" t="n">
         <v>68.48999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.9936127389780012</v>
+        <v>-0.9936127389779585</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.4507413330092</v>
+        <v>-1.450741333009138</v>
       </c>
     </row>
     <row r="57">
@@ -1724,16 +1724,16 @@
         <v>2019</v>
       </c>
       <c r="C59" t="n">
-        <v>66.63198114718615</v>
+        <v>66.63198114718617</v>
       </c>
       <c r="D59" t="n">
         <v>67.5</v>
       </c>
       <c r="E59" t="n">
-        <v>0.8680188528138473</v>
+        <v>0.8680188528138331</v>
       </c>
       <c r="F59" t="n">
-        <v>1.285953856020514</v>
+        <v>1.285953856020494</v>
       </c>
     </row>
     <row r="60">
@@ -1768,16 +1768,16 @@
         <v>2019</v>
       </c>
       <c r="C61" t="n">
-        <v>73.32422330954478</v>
+        <v>73.32422330954479</v>
       </c>
       <c r="D61" t="n">
         <v>73.66</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3357766904552193</v>
+        <v>0.3357766904552051</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4558467152528093</v>
+        <v>0.45584671525279</v>
       </c>
     </row>
     <row r="62">
@@ -1790,16 +1790,16 @@
         <v>2019</v>
       </c>
       <c r="C62" t="n">
-        <v>72.90056900720771</v>
+        <v>72.90056900720769</v>
       </c>
       <c r="D62" t="n">
         <v>73.22</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3194309927922916</v>
+        <v>0.3194309927923058</v>
       </c>
       <c r="F62" t="n">
-        <v>0.4362619404429003</v>
+        <v>0.4362619404429197</v>
       </c>
     </row>
     <row r="63">
@@ -1834,16 +1834,16 @@
         <v>2019</v>
       </c>
       <c r="C64" t="n">
-        <v>73.28917879216506</v>
+        <v>73.28917879216505</v>
       </c>
       <c r="D64" t="n">
         <v>73.28</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.009178792165059235</v>
+        <v>-0.009178792165045024</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.01252564433004808</v>
+        <v>-0.01252564433002869</v>
       </c>
     </row>
     <row r="65">
@@ -1900,16 +1900,16 @@
         <v>2019</v>
       </c>
       <c r="C67" t="n">
-        <v>71.1750924352056</v>
+        <v>71.17509243520558</v>
       </c>
       <c r="D67" t="n">
         <v>71.66</v>
       </c>
       <c r="E67" t="n">
-        <v>0.4849075647943977</v>
+        <v>0.4849075647944119</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6766781534948335</v>
+        <v>0.6766781534948534</v>
       </c>
     </row>
     <row r="68">
@@ -1922,16 +1922,16 @@
         <v>2019</v>
       </c>
       <c r="C68" t="n">
-        <v>74.3059068653277</v>
+        <v>74.30590686532771</v>
       </c>
       <c r="D68" t="n">
         <v>74.77</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4640931346722965</v>
+        <v>0.4640931346722823</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6206943087766438</v>
+        <v>0.6206943087766248</v>
       </c>
     </row>
     <row r="69">
@@ -1944,16 +1944,16 @@
         <v>2019</v>
       </c>
       <c r="C69" t="n">
-        <v>72.83334794910434</v>
+        <v>72.83334794910432</v>
       </c>
       <c r="D69" t="n">
         <v>73.43000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>0.5966520508956705</v>
+        <v>0.5966520508956847</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8125453505320311</v>
+        <v>0.8125453505320506</v>
       </c>
     </row>
     <row r="70">
@@ -1966,16 +1966,16 @@
         <v>2019</v>
       </c>
       <c r="C70" t="n">
-        <v>70.66759610343152</v>
+        <v>70.66759610343151</v>
       </c>
       <c r="D70" t="n">
         <v>71.2</v>
       </c>
       <c r="E70" t="n">
-        <v>0.5324038965684821</v>
+        <v>0.5324038965684963</v>
       </c>
       <c r="F70" t="n">
-        <v>0.7477582816973063</v>
+        <v>0.7477582816973263</v>
       </c>
     </row>
     <row r="71">
@@ -1988,16 +1988,16 @@
         <v>2019</v>
       </c>
       <c r="C71" t="n">
-        <v>72.93613433787769</v>
+        <v>72.93613433787766</v>
       </c>
       <c r="D71" t="n">
         <v>72.93000000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.006134337877682583</v>
+        <v>-0.006134337877654161</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.008411268171784701</v>
+        <v>-0.00841126817174573</v>
       </c>
     </row>
     <row r="72">
@@ -2032,16 +2032,16 @@
         <v>2019</v>
       </c>
       <c r="C73" t="n">
-        <v>73.71372643085654</v>
+        <v>73.71372643085655</v>
       </c>
       <c r="D73" t="n">
         <v>74.37</v>
       </c>
       <c r="E73" t="n">
-        <v>0.6562735691434654</v>
+        <v>0.6562735691434511</v>
       </c>
       <c r="F73" t="n">
-        <v>0.882443954744474</v>
+        <v>0.8824439547444549</v>
       </c>
     </row>
     <row r="74">
@@ -2076,16 +2076,16 @@
         <v>2019</v>
       </c>
       <c r="C75" t="n">
-        <v>72.2676889297598</v>
+        <v>72.26768892975981</v>
       </c>
       <c r="D75" t="n">
         <v>72.76000000000001</v>
       </c>
       <c r="E75" t="n">
-        <v>0.4923110702402056</v>
+        <v>0.4923110702401914</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6766232411217779</v>
+        <v>0.6766232411217583</v>
       </c>
     </row>
     <row r="76">
@@ -2098,16 +2098,16 @@
         <v>2019</v>
       </c>
       <c r="C76" t="n">
-        <v>70.46687404159708</v>
+        <v>70.46687404159704</v>
       </c>
       <c r="D76" t="n">
         <v>70.20999999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.2568740415970865</v>
+        <v>-0.2568740415970439</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.3658653206054501</v>
+        <v>-0.3658653206053893</v>
       </c>
     </row>
     <row r="77">
@@ -2164,16 +2164,16 @@
         <v>2019</v>
       </c>
       <c r="C79" t="n">
-        <v>75.29215031565657</v>
+        <v>75.29215031565658</v>
       </c>
       <c r="D79" t="n">
         <v>75.53</v>
       </c>
       <c r="E79" t="n">
-        <v>0.2378496843434306</v>
+        <v>0.2378496843434164</v>
       </c>
       <c r="F79" t="n">
-        <v>0.3149075656605727</v>
+        <v>0.3149075656605539</v>
       </c>
     </row>
     <row r="80">
@@ -2186,16 +2186,16 @@
         <v>2019</v>
       </c>
       <c r="C80" t="n">
-        <v>73.05336455209502</v>
+        <v>73.05336455209498</v>
       </c>
       <c r="D80" t="n">
         <v>73.34</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2866354479049846</v>
+        <v>0.2866354479050273</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3908309897804535</v>
+        <v>0.3908309897805116</v>
       </c>
     </row>
     <row r="81">
@@ -2208,16 +2208,16 @@
         <v>2019</v>
       </c>
       <c r="C81" t="n">
-        <v>64.41197267496391</v>
+        <v>64.41197267496392</v>
       </c>
       <c r="D81" t="n">
         <v>67.26000000000001</v>
       </c>
       <c r="E81" t="n">
-        <v>2.848027325036099</v>
+        <v>2.848027325036085</v>
       </c>
       <c r="F81" t="n">
-        <v>4.234355226042371</v>
+        <v>4.234355226042351</v>
       </c>
     </row>
     <row r="82">
@@ -2252,16 +2252,16 @@
         <v>2019</v>
       </c>
       <c r="C83" t="n">
-        <v>72.28031189156869</v>
+        <v>72.28031189156872</v>
       </c>
       <c r="D83" t="n">
         <v>72.73999999999999</v>
       </c>
       <c r="E83" t="n">
-        <v>0.4596881084313083</v>
+        <v>0.4596881084312798</v>
       </c>
       <c r="F83" t="n">
-        <v>0.6319605559957496</v>
+        <v>0.6319605559957105</v>
       </c>
     </row>
     <row r="84">
@@ -2296,16 +2296,16 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>75.70435106265084</v>
+        <v>75.70435106265082</v>
       </c>
       <c r="D85" t="n">
         <v>76.38</v>
       </c>
       <c r="E85" t="n">
-        <v>0.6756489373491519</v>
+        <v>0.6756489373491803</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8845888155919768</v>
+        <v>0.8845888155920141</v>
       </c>
     </row>
     <row r="86">
